--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_963_Spain_Northwest.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_963_Spain_Northwest.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rfd50b01099a74403"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R9238cc9316574942"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rb9cd8cb9f78c4245"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R1b40ee35bd604c8d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R6790210708ed46f7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rf86c758034b84240"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R4374b8770c754bf1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R25b2d1c29f3a43a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Ra2ba4ea977114a7c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R5eebf818a8874a2b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R6062a6ffdebd4887"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rf4bfc06107aa48b5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ963CommercialTable" displayName="EEZ963CommercialTable" ref="A1:O13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O13"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ963CommercialTable" displayName="EEZ963CommercialTable" ref="A1:E13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E13"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ963FunctionalTable" displayName="EEZ963FunctionalTable" ref="A1:O27" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O27"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ963FunctionalTable" displayName="EEZ963FunctionalTable" ref="A1:E27" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E27"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ963ValidationTable" displayName="EEZ963ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ963ValidationTable" displayName="EEZ963ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -21598,7 +21552,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2ca09e1d753449dd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R079eeb1865fc4ec3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21608,20 +21562,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -21629,714 +21573,250 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>12442.0459115962</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>12442.0459115962</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$313,A2,'Species'!$U$2:$U$313))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>1602846.006775919</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>1602846.006775919</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>62407.6279853657</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.333772830621041</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2156.6160381948002</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>62407.6279853657</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2287.1727001475806</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$313,A3,'Species'!$U$2:$U$313))</x:f>
-        <x:v>142737023.0090946</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.333772830621041</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2156.6160381948002</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>134589291.41893432</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>8147731.5901602805</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0605377404417633</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.06053774044176326</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>412.31370274359995</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>2.928795602519935</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>84.87809085714925</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>412.31370274359995</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>95.9557860260408</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$313,A4,'Species'!$U$2:$U$313))</x:f>
-        <x:v>39563.88543606947</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>2.928795602519935</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>84.87809085714925</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>34996.3999231189</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>4567.485512950567</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.1305130105663597</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.1305130105663597</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>2660.0517784703998</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.9160556545960485</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>824.2437346209783</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>2660.0517784703998</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>883.1160465380283</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$313,A5,'Species'!$U$2:$U$313))</x:f>
-        <x:v>2349134.4101892305</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.9160556545960485</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>824.2437346209783</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>2192531.0121716177</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>156603.39801761275</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0714258531114245</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.07142585311142445</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>8079.4288996141</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.077152207027848</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>119.44066343742233</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>8079.4288996141</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>131.11020506598268</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$313,A6,'Species'!$U$2:$U$313))</x:f>
-        <x:v>1059295.5798444315</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.077152207027848</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>119.44066343742233</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>965012.3479653912</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>94283.23187904025</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0977015807909865</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.0977015807909865</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>566.8937692769</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.06389673225753</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>11.585018516284688</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>566.8937692769</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>13.494662709988425</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$313,A7,'Species'!$U$2:$U$313))</x:f>
-        <x:v>7650.040208785765</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.06389673225753</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>11.585018516284688</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>6567.474813839306</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>1082.5653949464586</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.164837388133598</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.16483738813359794</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>42886.8511639813</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.4939335002799514</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>311.8412052339385</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>42886.8511639813</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>592.0346108450262</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$313,A8,'Species'!$U$2:$U$313))</x:f>
-        <x:v>25390500.239236232</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.4939335002799514</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>311.8412052339385</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>13373887.355664467</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>12016612.883571764</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.8985130922672357</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.8985130922672357</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>55098.35376173869</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.588520519425852</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>387.7220670628703</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>55098.35376173869</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>492.11412410641617</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$313,A9,'Species'!$U$2:$U$313))</x:f>
-        <x:v>27114678.101163495</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.588520519425852</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>387.7220670628703</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>21362847.6122626</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>5751830.488900896</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.2692445592131294</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.26924455921312934</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>625.1618504999</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.176479989298119</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1501.3432277536133</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>625.1618504999</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>2114.446120156855</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$313,A10,'Species'!$U$2:$U$313))</x:f>
-        <x:v>1321871.0492595935</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.176479989298119</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1501.3432277536133</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>938582.5104979416</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>383288.53876165184</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.4083695727063013</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.40836957270630114</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>1344.0071435886998</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.708175323353763</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>510.7111308865837</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>1344.0071435886998</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>561.4869092621653</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$313,A11,'Species'!$U$2:$U$313))</x:f>
-        <x:v>754642.4170798904</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.708175323353763</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>510.7111308865837</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>686399.408221832</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>68243.00885805837</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.099421718667921</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.09942171866792089</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>4594.6461932521</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.174207857830393</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>1493.5090474243812</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>4594.6461932521</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>1690.1247262744782</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$313,A12,'Species'!$U$2:$U$313))</x:f>
-        <x:v>7765525.139698278</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.174207857830393</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>1493.5090474243812</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>6862145.659336003</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>903379.4803622756</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.131646794633865</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.1316467946338651</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>3374.6031431352003</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.369286119273141</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>2340.3786049942046</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>3374.6031431352003</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>2396.558303426282</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$H$2:$H$313,A13,'Species'!$U$2:$U$313))</x:f>
-        <x:v>8087433.183449093</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.369286119273141</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>2340.3786049942046</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>7897848.996539818</x:v>
       </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>189584.18690927513</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.024004534271589</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.024004534271589033</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G13">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O13">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra5b9a04f4c004408"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd5a1f0632a9447e6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22346,20 +21826,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -22367,1470 +21837,516 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>2241.6243983747004</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.7811031385969356</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>604.0920753881721</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>2241.6243983747004</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>712.9123942224936</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$313,A2,'Species'!$U$2:$U$313))</x:f>
-        <x:v>1598081.8167928646</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.7811031385969356</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>604.0920753881721</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>1354147.5350549356</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>243934.28173792898</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.1801386299669578</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.18013862996695773</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>681.9247341896</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.066741975909677</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1166.1165951932162</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>681.9247341896</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>1574.4723907226912</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$313,A3,'Species'!$U$2:$U$313))</x:f>
-        <x:v>1073671.6665324352</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.066741975909677</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1166.1165951932162</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>795203.7492112154</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>278467.9173212198</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.3501843616776705</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.3501843616776705</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large bathypelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>937.4597887527999</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.547206638772614</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>352.538570178741</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>937.4597887527999</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>363.30548658473657</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$313,A4,'Species'!$U$2:$U$313))</x:f>
-        <x:v>340584.2847064603</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.547206638772614</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>352.538570178741</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>330490.73352697666</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>10093.55117948365</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0305411019297452</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.030541101929745188</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>1070.5532269508</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.2280909367080985</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>1690.794929299449</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>1070.5532269508</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2088.0114775276224</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$313,A5,'Species'!$U$2:$U$313))</x:f>
-        <x:v>2235327.4251775043</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.2280909367080985</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>1690.794929299449</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>1810085.967673575</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>425241.45750392927</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.2349288735995636</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.23492887359956371</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>49800.1762052275</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.410726791137418</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2574.70093742832</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>49800.1762052275</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2593.161105874708</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$313,A6,'Species'!$U$2:$U$313))</x:f>
-        <x:v>129139880.00110307</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.410726791137418</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2574.70093742832</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>128220560.35969475</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>919319.6414083242</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0071698301647518</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.007169830164751846</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large flatfishes (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>31.2457568114</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.247783131895826</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>1769.2252622097358</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>31.2457568114</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>2075.7277617579625</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$313,A7,'Species'!$U$2:$U$313))</x:f>
-        <x:v>64857.68485056094</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.247783131895826</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>1769.2252622097358</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>55280.7822875908</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>9576.902562970135</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.1732410824642023</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.17324108246420236</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>2778.5083673227996</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.3544099564307235</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>2261.5695931932605</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>2778.5083673227996</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>2299.7244019928567</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$313,A8,'Species'!$U$2:$U$313))</x:f>
-        <x:v>6389803.493473574</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.3544099564307235</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>2261.5695931932605</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>6283790.037970294</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>106013.45550327934</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0168709417187214</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.01687094171872146</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>272.4915182246</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.717770901335181</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>522.1206876673652</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>272.4915182246</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>555.0020043343005</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$313,A9,'Species'!$U$2:$U$313))</x:f>
-        <x:v>151233.33877874957</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.717770901335181</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>522.1206876673652</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>142273.45887895254</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>8959.87989979703</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0629764677853244</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.0629764677853244</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>248.10719224660002</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.8845532072884095</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>766.5724505039651</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>248.10719224660002</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>784.9594848593331</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$313,A10,'Species'!$U$2:$U$313))</x:f>
-        <x:v>194754.09381578668</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.8845532072884095</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>766.5724505039651</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>190192.13834813455</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>4561.955467652122</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.023986035949087</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.0239860359490872</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>3568.6031928701996</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.267842865306506</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>1852.8611073207485</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>3568.6031928701996</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>1957.0916726966193</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$313,A11,'Species'!$U$2:$U$313))</x:f>
-        <x:v>6984083.591924835</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.267842865306506</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>1852.8611073207485</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>6612126.063529837</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>371957.52839499805</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0562538470714564</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.05625384707145634</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>125.91583559539998</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>2.9567459054928364</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>90.52028350904816</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>125.91583559539998</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>111.28426546857877</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$313,A12,'Species'!$U$2:$U$313))</x:f>
-        <x:v>14012.451275096411</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>2.9567459054928364</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>90.52028350904816</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>11397.937136374303</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>2614.5141387221083</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.229384853367755</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.22938485336775497</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>3871.2439286924</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.312866309860233</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>2055.257822572043</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>3871.2439286924</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>2479.1010869910697</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$313,A13,'Species'!$U$2:$U$313))</x:f>
-        <x:v>9597205.031628909</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.312866309860233</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>2055.257822572043</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>7956404.367529584</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>1640800.6640993245</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.2062238906302325</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.20622389063023241</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium bathypelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>615.6789092289</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>4.067358755277863</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>1167.7738753428246</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>615.6789092289</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>1178.0141912482088</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$313,A14,'Species'!$U$2:$U$313))</x:f>
-        <x:v>725278.492323862</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>4.067358755277863</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>1167.7738753428246</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>718973.7457970757</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>6304.746526786359</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.008769091449642</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.008769091449642196</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>15425.8079455942</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>4.034502634409837</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>1082.6862826312902</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>15425.8079455942</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>1264.190778601588</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$313,A15,'Species'!$U$2:$U$313))</x:f>
-        <x:v>19501164.157299295</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>4.034502634409837</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>1082.6862826312902</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>16701310.661199605</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>2799853.49609969</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.1676427409139987</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.16764274091399872</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>36366.3618913217</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.215740700131075</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>164.3390227647853</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>36366.3618913217</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>188.22391108565986</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$313,A16,'Species'!$U$2:$U$313))</x:f>
-        <x:v>6845018.867141065</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.215740700131075</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>164.3390227647853</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>5976412.374730337</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>868606.4924107278</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.1453391161699948</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.14533911616999493</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>51096.8257245943</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.686970340957808</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>486.37398887696764</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>51096.8257245943</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>543.5935024968419</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$313,A17,'Species'!$U$2:$U$313))</x:f>
-        <x:v>27775902.462102946</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.686970340957808</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>486.37398887696764</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>24852166.94662218</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>2923735.515480764</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.1176450939574163</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.11764509395741637</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>121.41927163299998</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.110857400883434</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>129.07953757516066</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>121.41927163299998</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>166.50273734401551</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$313,A18,'Species'!$U$2:$U$313))</x:f>
-        <x:v>20216.64109321107</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.110857400883434</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>129.07953757516066</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>15672.74343510046</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>4543.897658110611</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.2899235655152856</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.28992356551528564</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>823.18277635</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>2.2716252062201554</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>18.690684482396115</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>823.18277635</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>31.41444981588032</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$313,A19,'Species'!$U$2:$U$313))</x:f>
-        <x:v>25859.83401694411</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>2.2716252062201554</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>18.690684482396115</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>15385.849544100698</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>10473.984472843413</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.6807543803689013</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.6807543803689012</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>120.51899080410001</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>2.801589997026199</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>63.327157833097544</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>120.51899080410001</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>74.37455679605729</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$313,A20,'Species'!$U$2:$U$313))</x:f>
-        <x:v>8963.546526563043</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>2.801589997026199</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>63.327157833097544</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>7632.125152536873</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>1331.4213740261694</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.1744496254209895</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.17444962542098943</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>200.9776691875</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.3802978178359115</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>240.04784850349108</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>200.9776691875</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>240.10291529685466</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$313,A21,'Species'!$U$2:$U$313))</x:f>
-        <x:v>48255.32428148559</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.3802978178359115</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>240.04784850349108</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>48244.25708570575</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>11.067195779840404</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.0002293992373057</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.0002293992373056874</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>12.1018857225</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>3.919184401791727</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>830.2031976438569</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>12.1018857225</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>831.0383850153322</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$313,A22,'Species'!$U$2:$U$313))</x:f>
-        <x:v>10057.131566466507</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>3.919184401791727</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>830.2031976438569</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>10047.024224340039</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>10.107342126468211</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1.0010060035589425</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0.0010060035589425618</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
       <x:c r="A23" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B23" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D23" s="31" t="n">
+      <x:c r="B23" s="31" t="n">
         <x:v>20697.422386034403</x:v>
       </x:c>
+      <x:c r="C23" s="32" t="n">
+        <x:v>3.0930394357235365</x:v>
+      </x:c>
+      <x:c r="D23" s="32" t="n">
+        <x:f>IF(C23="","",(1/'Metadata'!$B$5)^(C23-1))</x:f>
+        <x:v>123.89090794581554</x:v>
+      </x:c>
       <x:c r="E23" s="31" t="n">
-        <x:v>20697.422386034403</x:v>
-      </x:c>
-      <x:c r="F23" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H23" s="32" t="n">
-        <x:f>IF(E23=0,"",I23/E23)</x:f>
-        <x:v>124.20289905476905</x:v>
-      </x:c>
-      <x:c r="I23" s="31" t="n">
-        <x:f>IF(C23=0,"",SUMIF('Species'!$G$2:$G$313,A23,'Species'!$U$2:$U$313))</x:f>
-        <x:v>2570679.863306548</x:v>
-      </x:c>
-      <x:c r="J23" s="32" t="n">
-        <x:v>3.0930394357235365</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
-        <x:f>IF(J23="","",(1/'Metadata'!$B$5)^(J23-1))</x:f>
-        <x:v>123.89090794581554</x:v>
-      </x:c>
-      <x:c r="L23" s="31" t="n">
-        <x:f>IF(E23=0,"",E23*K23)</x:f>
+        <x:f>IF(B23=0,"",B23*D23)</x:f>
         <x:v>2564222.45154385</x:v>
-      </x:c>
-      <x:c r="M23" s="31" t="n">
-        <x:f>IF(E23=0,"",I23-L23)</x:f>
-        <x:v>6457.411762698088</x:v>
-      </x:c>
-      <x:c r="N23" s="32" t="n">
-        <x:f>IF(L23=0,"",I23/L23)</x:f>
-        <x:v>1.0025182728428301</x:v>
-      </x:c>
-      <x:c r="O23" s="34" t="n">
-        <x:f>IF(L23=0,"",M23/L23)</x:f>
-        <x:v>0.0025182728428300954</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="18" customHeight="1">
       <x:c r="A24" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B24" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C24" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D24" s="31" t="n">
+      <x:c r="B24" s="31" t="n">
         <x:v>1.4762037171</x:v>
       </x:c>
+      <x:c r="C24" s="32" t="n">
+        <x:v>3.723990357904376</x:v>
+      </x:c>
+      <x:c r="D24" s="32" t="n">
+        <x:f>IF(C24="","",(1/'Metadata'!$B$5)^(C24-1))</x:f>
+        <x:v>529.6516845691363</x:v>
+      </x:c>
       <x:c r="E24" s="31" t="n">
-        <x:v>1.4762037171</x:v>
-      </x:c>
-      <x:c r="F24" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G24" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H24" s="32" t="n">
-        <x:f>IF(E24=0,"",I24/E24)</x:f>
-        <x:v>533.0750592467</x:v>
-      </x:c>
-      <x:c r="I24" s="31" t="n">
-        <x:f>IF(C24=0,"",SUMIF('Species'!$G$2:$G$313,A24,'Species'!$U$2:$U$313))</x:f>
-        <x:v>786.9273839532813</x:v>
-      </x:c>
-      <x:c r="J24" s="32" t="n">
-        <x:v>3.723990357904376</x:v>
-      </x:c>
-      <x:c r="K24" s="32" t="n">
-        <x:f>IF(J24="","",(1/'Metadata'!$B$5)^(J24-1))</x:f>
-        <x:v>529.6516845691363</x:v>
-      </x:c>
-      <x:c r="L24" s="31" t="n">
-        <x:f>IF(E24=0,"",E24*K24)</x:f>
+        <x:f>IF(B24=0,"",B24*D24)</x:f>
         <x:v>781.8737855292356</x:v>
-      </x:c>
-      <x:c r="M24" s="31" t="n">
-        <x:f>IF(E24=0,"",I24-L24)</x:f>
-        <x:v>5.053598424045617</x:v>
-      </x:c>
-      <x:c r="N24" s="32" t="n">
-        <x:f>IF(L24=0,"",I24/L24)</x:f>
-        <x:v>1.0064634452741308</x:v>
-      </x:c>
-      <x:c r="O24" s="34" t="n">
-        <x:f>IF(L24=0,"",M24/L24)</x:f>
-        <x:v>0.006463445274130698</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="18" customHeight="1">
       <x:c r="A25" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B25" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C25" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D25" s="31" t="n">
+      <x:c r="B25" s="31" t="n">
         <x:v>2628.8060216589997</x:v>
       </x:c>
+      <x:c r="C25" s="32" t="n">
+        <x:v>3.91211277102154</x:v>
+      </x:c>
+      <x:c r="D25" s="32" t="n">
+        <x:f>IF(C25="","",(1/'Metadata'!$B$5)^(C25-1))</x:f>
+        <x:v>816.7944366482047</x:v>
+      </x:c>
       <x:c r="E25" s="31" t="n">
-        <x:v>2628.8060216589997</x:v>
-      </x:c>
-      <x:c r="F25" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G25" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H25" s="32" t="n">
-        <x:f>IF(E25=0,"",I25/E25)</x:f>
-        <x:v>868.9407687437878</x:v>
-      </x:c>
-      <x:c r="I25" s="31" t="n">
-        <x:f>IF(C25=0,"",SUMIF('Species'!$G$2:$G$313,A25,'Species'!$U$2:$U$313))</x:f>
-        <x:v>2284276.7253386695</x:v>
-      </x:c>
-      <x:c r="J25" s="32" t="n">
-        <x:v>3.91211277102154</x:v>
-      </x:c>
-      <x:c r="K25" s="32" t="n">
-        <x:f>IF(J25="","",(1/'Metadata'!$B$5)^(J25-1))</x:f>
-        <x:v>816.7944366482047</x:v>
-      </x:c>
-      <x:c r="L25" s="31" t="n">
-        <x:f>IF(E25=0,"",E25*K25)</x:f>
+        <x:f>IF(B25=0,"",B25*D25)</x:f>
         <x:v>2147194.133518371</x:v>
-      </x:c>
-      <x:c r="M25" s="31" t="n">
-        <x:f>IF(E25=0,"",I25-L25)</x:f>
-        <x:v>137082.5918202987</x:v>
-      </x:c>
-      <x:c r="N25" s="32" t="n">
-        <x:f>IF(L25=0,"",I25/L25)</x:f>
-        <x:v>1.063842663166966</x:v>
-      </x:c>
-      <x:c r="O25" s="34" t="n">
-        <x:f>IF(L25=0,"",M25/L25)</x:f>
-        <x:v>0.06384266316696596</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="18" customHeight="1">
       <x:c r="A26" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B26" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C26" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D26" s="31" t="n">
+      <x:c r="B26" s="31" t="n">
         <x:v>415.28426105319994</x:v>
       </x:c>
+      <x:c r="C26" s="32" t="n">
+        <x:v>3.895759125476255</x:v>
+      </x:c>
+      <x:c r="D26" s="32" t="n">
+        <x:f>IF(C26="","",(1/'Metadata'!$B$5)^(C26-1))</x:f>
+        <x:v>786.6093883043176</x:v>
+      </x:c>
       <x:c r="E26" s="31" t="n">
-        <x:v>415.28426105319994</x:v>
-      </x:c>
-      <x:c r="F26" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G26" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H26" s="32" t="n">
-        <x:f>IF(E26=0,"",I26/E26)</x:f>
-        <x:v>863.345655526382</x:v>
-      </x:c>
-      <x:c r="I26" s="31" t="n">
-        <x:f>IF(C26=0,"",SUMIF('Species'!$G$2:$G$313,A26,'Species'!$U$2:$U$313))</x:f>
-        <x:v>358533.86258876405</x:v>
-      </x:c>
-      <x:c r="J26" s="32" t="n">
-        <x:v>3.895759125476255</x:v>
-      </x:c>
-      <x:c r="K26" s="32" t="n">
-        <x:f>IF(J26="","",(1/'Metadata'!$B$5)^(J26-1))</x:f>
-        <x:v>786.6093883043176</x:v>
-      </x:c>
-      <x:c r="L26" s="31" t="n">
-        <x:f>IF(E26=0,"",E26*K26)</x:f>
+        <x:f>IF(B26=0,"",B26*D26)</x:f>
         <x:v>326666.49855946813</x:v>
-      </x:c>
-      <x:c r="M26" s="31" t="n">
-        <x:f>IF(E26=0,"",I26-L26)</x:f>
-        <x:v>31867.364029295917</x:v>
-      </x:c>
-      <x:c r="N26" s="32" t="n">
-        <x:f>IF(L26=0,"",I26/L26)</x:f>
-        <x:v>1.097553205393955</x:v>
-      </x:c>
-      <x:c r="O26" s="34" t="n">
-        <x:f>IF(L26=0,"",M26/L26)</x:f>
-        <x:v>0.09755320539395505</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="18" customHeight="1">
       <x:c r="A27" s="24" t="str">
         <x:v>Small to medium sharks (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B27" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C27" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D27" s="31" t="n">
+      <x:c r="B27" s="31" t="n">
         <x:v>338.2672211041</x:v>
       </x:c>
+      <x:c r="C27" s="32" t="n">
+        <x:v>3.8959201448491068</x:v>
+      </x:c>
+      <x:c r="D27" s="32" t="n">
+        <x:f>IF(C27="","",(1/'Metadata'!$B$5)^(C27-1))</x:f>
+        <x:v>786.9010863081522</x:v>
+      </x:c>
       <x:c r="E27" s="31" t="n">
-        <x:v>338.2672211041</x:v>
-      </x:c>
-      <x:c r="F27" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G27" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H27" s="32" t="n">
-        <x:f>IF(E27=0,"",I27/E27)</x:f>
-        <x:v>803.1353008996578</x:v>
-      </x:c>
-      <x:c r="I27" s="31" t="n">
-        <x:f>IF(C27=0,"",SUMIF('Species'!$G$2:$G$313,A27,'Species'!$U$2:$U$313))</x:f>
-        <x:v>271674.3464059324</x:v>
-      </x:c>
-      <x:c r="J27" s="32" t="n">
-        <x:v>3.8959201448491068</x:v>
-      </x:c>
-      <x:c r="K27" s="32" t="n">
-        <x:f>IF(J27="","",(1/'Metadata'!$B$5)^(J27-1))</x:f>
-        <x:v>786.9010863081522</x:v>
-      </x:c>
-      <x:c r="L27" s="31" t="n">
-        <x:f>IF(E27=0,"",E27*K27)</x:f>
+        <x:f>IF(B27=0,"",B27*D27)</x:f>
         <x:v>266182.84374925616</x:v>
       </x:c>
-      <x:c r="M27" s="31" t="n">
-        <x:f>IF(E27=0,"",I27-L27)</x:f>
-        <x:v>5491.502656676224</x:v>
-      </x:c>
-      <x:c r="N27" s="32" t="n">
-        <x:f>IF(L27=0,"",I27/L27)</x:f>
-        <x:v>1.0206305657394255</x:v>
-      </x:c>
-      <x:c r="O27" s="34" t="n">
-        <x:f>IF(L27=0,"",M27/L27)</x:f>
-        <x:v>0.020630565739425386</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G27">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O27">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb18f41f82fae43b5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R321464b0ec1c4510"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24005,7 +22521,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -24104,7 +22620,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>218230163.06143558</x:v>
+        <x:v>190512956.20310688</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -24118,7 +22634,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>218230163.06143552</x:v>
+        <x:v>207412846.6597897</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -24132,7 +22648,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-27717206.8583287</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -24146,7 +22662,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>-5.960464477539063e-8</x:v>
+        <x:v>-10817316.401645869</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -24157,9 +22673,9 @@
         <x:v>EEZ_963</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -24171,47 +22687,19 @@
         <x:v>EEZ_963</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_963</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_963</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R92d7cd3d744e42cd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R30b0860e0bce4f06"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24258,7 +22746,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
